--- a/input.xlsx
+++ b/input.xlsx
@@ -8,11 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="Selected_Stocks" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
-    <sheet name="Benchmark_Stocks" sheetId="2" r:id="rId3"/>
+    <sheet name="Benchmark_Stocks" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Benchmark_Stocks!$A$1:$A$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Benchmark_Stocks!$A$1:$A$102</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="112">
   <si>
     <t>Ticker</t>
   </si>
@@ -677,7 +676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -687,17 +686,297 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>105</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>106</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -706,316 +985,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A60"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>96</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/input.xlsx
+++ b/input.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="113">
   <si>
     <t>Ticker</t>
   </si>
@@ -359,6 +359,9 @@
   </si>
   <si>
     <t>MISR</t>
+  </si>
+  <si>
+    <t>LUTS</t>
   </si>
 </sst>
 </file>
@@ -676,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A60"/>
+  <dimension ref="A1:A61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -977,6 +980,11 @@
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>96</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/input.xlsx
+++ b/input.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="116">
   <si>
     <t>Ticker</t>
   </si>
@@ -362,6 +362,15 @@
   </si>
   <si>
     <t>LUTS</t>
+  </si>
+  <si>
+    <t>HBCO</t>
+  </si>
+  <si>
+    <t>INFI</t>
+  </si>
+  <si>
+    <t>EPCO</t>
   </si>
 </sst>
 </file>
@@ -679,7 +688,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A61"/>
+  <dimension ref="A1:A64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -985,6 +994,21 @@
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>112</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/input.xlsx
+++ b/input.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="117">
   <si>
     <t>Ticker</t>
   </si>
@@ -371,6 +371,9 @@
   </si>
   <si>
     <t>EPCO</t>
+  </si>
+  <si>
+    <t>EGAS</t>
   </si>
 </sst>
 </file>
@@ -688,7 +691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A64"/>
+  <dimension ref="A1:A65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -1009,6 +1012,11 @@
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>115</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/input.xlsx
+++ b/input.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="11880"/>
   </bookViews>
   <sheets>
     <sheet name="Selected_Stocks" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="123">
   <si>
     <t>Ticker</t>
   </si>
@@ -374,6 +374,24 @@
   </si>
   <si>
     <t>EGAS</t>
+  </si>
+  <si>
+    <t>EGX70</t>
+  </si>
+  <si>
+    <t>EGX30</t>
+  </si>
+  <si>
+    <t>UNINDEX</t>
+  </si>
+  <si>
+    <t>EGX33</t>
+  </si>
+  <si>
+    <t>OLFI</t>
+  </si>
+  <si>
+    <t>INDEX</t>
   </si>
 </sst>
 </file>
@@ -691,336 +709,556 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A65"/>
+  <dimension ref="A1:B68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>116</v>
       </c>
+      <c r="B65" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>14</v>
+      </c>
+      <c r="B66" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>121</v>
+      </c>
+      <c r="B67" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>44</v>
+      </c>
+      <c r="B68" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/input.xlsx
+++ b/input.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="124">
   <si>
     <t>Ticker</t>
   </si>
@@ -392,6 +392,9 @@
   </si>
   <si>
     <t>INDEX</t>
+  </si>
+  <si>
+    <t>MBEG</t>
   </si>
 </sst>
 </file>
@@ -709,7 +712,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B68"/>
+  <dimension ref="A1:B69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1254,6 +1257,14 @@
       </c>
       <c r="B68" t="s">
         <v>118</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>123</v>
+      </c>
+      <c r="B69" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/input.xlsx
+++ b/input.xlsx
@@ -394,7 +394,7 @@
     <t>INDEX</t>
   </si>
   <si>
-    <t>MBEG</t>
+    <t>COPR</t>
   </si>
 </sst>
 </file>
